--- a/study_case_model/smaller_network/scenario_variables/price_scenarios111.xlsx
+++ b/study_case_model/smaller_network/scenario_variables/price_scenarios111.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,6 +448,54 @@
         <is>
           <t>price</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>33.94450875984197</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ST.FERGUS</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>25.27932666832201</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>27.21604148899499</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/smaller_network/scenario_variables/price_scenarios111.xlsx
+++ b/study_case_model/smaller_network/scenario_variables/price_scenarios111.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,45 +457,11 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ZEEBRUGGE</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>33.94450875984197</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ST.FERGUS</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>25.27932666832201</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>DORNUM</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>27.21604148899499</v>
+        <v>27.83035930181793</v>
       </c>
     </row>
   </sheetData>
